--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260625.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.74%</t>
+          <t>26.64%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>8.73%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.77%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.16%</t>
+          <t>7.31%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>68,880</t>
+          <t>22,895</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,895</t>
+          <t>68,880</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -924,95 +924,95 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>22,600</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>22,600</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>30,798</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>30,798</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>147,015</t>
+          <t>21,455</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,455</t>
+          <t>147,015</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1210,51 +1210,51 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,942,745</t>
+          <t>13,665</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,665</t>
+          <t>1,942,745</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,29 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>31,854,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
